--- a/louvers/files/reference_xls/price_xls/grille.xlsx
+++ b/louvers/files/reference_xls/price_xls/grille.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B39F595-3DE7-1B4A-B728-5E7DEEC7FC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5CF31-49BC-FF43-9B7F-FA2349A96E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="2" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Price" sheetId="1" r:id="rId1"/>
@@ -1164,39 +1164,39 @@
       </c>
       <c r="B2" s="28">
         <f>C2/10.7639104</f>
-        <v>565.77951447830708</v>
+        <v>622.35746592613782</v>
       </c>
       <c r="C2" s="29">
         <f>((1000/B8)*'Per m weight'!B3)*A8</f>
-        <v>6090.0000000000009</v>
+        <v>6699.0000000000009</v>
       </c>
       <c r="D2" s="30">
         <f>+A8*'Per m weight'!B3</f>
-        <v>304.5</v>
+        <v>334.95000000000005</v>
       </c>
       <c r="E2" s="40">
         <f>F2/10.7639104</f>
-        <v>666.57911143519004</v>
+        <v>723.15706288302079</v>
       </c>
       <c r="F2" s="41">
         <f>C2+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B8))*'Coating Rate'!C1)</f>
-        <v>7174.9978300000012</v>
+        <v>7783.9978300000012</v>
       </c>
       <c r="G2" s="42">
         <f>D2+((('Per m weight'!C3/25.4)*39.37008)*'Coating Rate'!C1)</f>
-        <v>358.75011023622045</v>
+        <v>389.2001102362205</v>
       </c>
       <c r="H2" s="52">
         <f>I2/10.7639104</f>
-        <v>807.6985471748261</v>
+        <v>864.27649862265673</v>
       </c>
       <c r="I2" s="53">
         <f>C2+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B8))*'Coating Rate'!C2)</f>
-        <v>8693.9947920000013</v>
+        <v>9302.9947920000013</v>
       </c>
       <c r="J2" s="54">
         <f>+D2+((('Per m weight'!C3/25.4)*39.37008)*'Coating Rate'!C2)</f>
-        <v>434.70026456692915</v>
+        <v>465.1502645669292</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1205,39 +1205,39 @@
       </c>
       <c r="B3" s="31">
         <f>C3/10.7639104</f>
-        <v>43.61797734771185</v>
+        <v>47.979775082483037</v>
       </c>
       <c r="C3" s="32">
         <f>(2*'Per m weight'!B4)*A8</f>
-        <v>469.5</v>
+        <v>516.45000000000005</v>
       </c>
       <c r="D3" s="33">
         <f>+A8*'Per m weight'!B4</f>
-        <v>234.75</v>
+        <v>258.22500000000002</v>
       </c>
       <c r="E3" s="43">
         <f t="shared" ref="E3:E4" si="0">F3/10.7639104</f>
-        <v>51.897944240598662</v>
+        <v>56.259741975369849</v>
       </c>
       <c r="F3" s="44">
         <f>C3+(((('Per m weight'!C4*0.03937)*39.37)*2)*'Coating Rate'!C1)</f>
-        <v>558.62482175000002</v>
+        <v>605.57482175000007</v>
       </c>
       <c r="G3" s="45">
         <f>+D3+((('Per m weight'!C4/25.4)*39.37008)*'Coating Rate'!C1)</f>
-        <v>279.31259055118107</v>
+        <v>302.7875905511811</v>
       </c>
       <c r="H3" s="55">
         <f t="shared" ref="H3:H4" si="1">I3/10.7639104</f>
-        <v>63.489897890640187</v>
+        <v>67.851695625411381</v>
       </c>
       <c r="I3" s="56">
         <f>C3+(((('Per m weight'!C4*0.03937)*39.37)*2)*'Coating Rate'!C2)</f>
-        <v>683.39957219999997</v>
+        <v>730.34957220000001</v>
       </c>
       <c r="J3" s="57">
         <f>+D3+((('Per m weight'!C4/25.4)*39.37008)*'Coating Rate'!C2)</f>
-        <v>341.70021732283465</v>
+        <v>365.17521732283467</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1246,39 +1246,39 @@
       </c>
       <c r="B4" s="34">
         <f>C4/10.7639104</f>
-        <v>15.747065304445492</v>
+        <v>17.321771834890043</v>
       </c>
       <c r="C4" s="35">
         <f>(2*'Per m weight'!B5)*A8</f>
-        <v>169.5</v>
+        <v>186.45000000000002</v>
       </c>
       <c r="D4" s="36">
         <f>+A8*'Per m weight'!B5</f>
-        <v>84.75</v>
+        <v>93.225000000000009</v>
       </c>
       <c r="E4" s="46">
         <f t="shared" si="0"/>
-        <v>18.62705378892786</v>
+        <v>20.201760319372411</v>
       </c>
       <c r="F4" s="47">
         <f>C4+(((('Per m weight'!C5*0.03937)*39.37)*2)*'Coating Rate'!C1)</f>
-        <v>200.49993799999999</v>
+        <v>217.44993800000003</v>
       </c>
       <c r="G4" s="48">
         <f>+D4+((('Per m weight'!C5/25.4)*39.37008)*'Coating Rate'!C1)</f>
-        <v>100.25003149606299</v>
+        <v>108.725031496063</v>
       </c>
       <c r="H4" s="58">
         <f t="shared" si="1"/>
-        <v>22.659037667203176</v>
+        <v>24.233744197647724</v>
       </c>
       <c r="I4" s="59">
         <f>C4+(((('Per m weight'!C5*0.03937)*39.37)*2)*'Coating Rate'!C2)</f>
-        <v>243.8998512</v>
+        <v>260.84985119999999</v>
       </c>
       <c r="J4" s="60">
         <f>+D4+((('Per m weight'!C5/25.4)*39.37008)*'Coating Rate'!C2)</f>
-        <v>121.95007559055118</v>
+        <v>130.42507559055119</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1287,29 +1287,29 @@
       </c>
       <c r="B5" s="37">
         <f t="shared" ref="B5:I5" si="2">SUM(B2:B4)</f>
-        <v>625.14455713046448</v>
+        <v>687.65901284351082</v>
       </c>
       <c r="C5" s="38">
         <f t="shared" si="2"/>
-        <v>6729.0000000000009</v>
+        <v>7401.9000000000005</v>
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="49">
         <f t="shared" si="2"/>
-        <v>737.10410946471654</v>
+        <v>799.618565177763</v>
       </c>
       <c r="F5" s="50">
         <f t="shared" si="2"/>
-        <v>7934.1225897500008</v>
+        <v>8607.0225897500004</v>
       </c>
       <c r="G5" s="51"/>
       <c r="H5" s="61">
         <f t="shared" si="2"/>
-        <v>893.8474827326695</v>
+        <v>956.36193844571585</v>
       </c>
       <c r="I5" s="62">
         <f t="shared" si="2"/>
-        <v>9621.2942154000011</v>
+        <v>10294.194215400003</v>
       </c>
       <c r="J5" s="63"/>
     </row>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B8" s="12">
         <v>50</v>
